--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
+          <t>浙江省宁波市海曙区环城南路西段2558号</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区环城南路西段2558号</t>
+          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>北京怀柔万达广场</t>
+          <t>北京湾里王府井</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>北京市怀柔区府前西街1号院1号楼1F</t>
+          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>北京湾里王府井</t>
+          <t>北京怀柔万达广场</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -12419,12 +12419,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
+          <t>北京市怀柔区府前西街1号院1号楼1F</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 13 期</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
+          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>上海市嘉定区澄浏中路886号</t>
+          <t>上海市青浦区盈顺路870号3幢1层</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
+          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>上海市青浦区盈顺路870号3幢1层</t>
+          <t>上海市嘉定区澄浏中路886号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -13322,17 +13322,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,14 +13374,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -13391,12 +13391,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,29 +13438,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13642,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -13839,12 +13839,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,14 +13854,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,29 +13886,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -13930,17 +13930,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
@@ -13994,17 +13994,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,29 +14014,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,29 +14046,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
@@ -14117,22 +14117,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14186,17 +14186,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14277,22 +14277,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14410,17 +14410,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -14442,17 +14442,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,29 +14462,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14494,29 +14494,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
@@ -14538,17 +14538,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -14570,17 +14570,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10718,7 +10718,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12067,12 +12067,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -13317,22 +13317,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13386,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,14 +13438,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
@@ -13514,17 +13514,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,14 +13566,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -13583,12 +13583,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13610,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13642,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
@@ -13674,17 +13674,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
@@ -13706,17 +13706,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
@@ -13829,22 +13829,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,29 +13886,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
@@ -13930,17 +13930,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
@@ -13994,17 +13994,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,29 +14014,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -14063,12 +14063,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14117,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -14127,12 +14127,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14282,17 +14282,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,7 +14309,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14341,7 +14341,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -14351,12 +14351,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14437,22 +14437,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,29 +14462,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14494,29 +14494,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14565,22 +14565,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
+          <t>小鹏汽车广州璟泰大厦销售中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>广州市海珠区阅江西路518号103铺</t>
+          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州璟泰大厦销售中心</t>
+          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
+          <t>广州市海珠区阅江西路518号103铺</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
+          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>上海市青浦区盈顺路870号3幢1层</t>
+          <t>上海市嘉定区澄浏中路886号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
+          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>上海市嘉定区澄浏中路886号</t>
+          <t>上海市青浦区盈顺路870号3幢1层</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -13349,22 +13349,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,29 +13374,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -13487,12 +13487,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,29 +13630,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
@@ -13706,17 +13706,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -13898,17 +13898,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -13930,17 +13930,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,29 +13982,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,29 +14014,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,29 +14046,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -14117,22 +14117,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14346,17 +14346,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14405,22 +14405,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,29 +14430,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,29 +14462,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14494,29 +14494,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区环城南路西段2558号</t>
+          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
+          <t>浙江省宁波市海曙区环城南路西段2558号</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州璟泰大厦销售中心</t>
+          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
+          <t>广州市海珠区阅江西路518号103铺</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
+          <t>小鹏汽车广州璟泰大厦销售中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>广州市海珠区阅江西路518号103铺</t>
+          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
+          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>上海市嘉定区澄浏中路886号</t>
+          <t>上海市青浦区盈顺路870号3幢1层</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
+          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>上海市青浦区盈顺路870号3幢1层</t>
+          <t>上海市嘉定区澄浏中路886号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,29 +13342,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,29 +13374,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13470,29 +13470,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,29 +13502,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,29 +13598,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,29 +13630,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13706,17 +13706,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -13802,17 +13802,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
@@ -13898,17 +13898,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,29 +13918,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -13962,17 +13962,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,29 +13982,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
@@ -14026,17 +14026,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,29 +14046,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
@@ -14149,22 +14149,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14186,17 +14186,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14213,22 +14213,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14282,17 +14282,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14341,22 +14341,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14410,17 +14410,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -14442,17 +14442,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -14533,22 +14533,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14558,29 +14558,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10718,7 +10718,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
+          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>上海市青浦区盈顺路870号3幢1层</t>
+          <t>上海市嘉定区澄浏中路886号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
+          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>上海市嘉定区澄浏中路886号</t>
+          <t>上海市青浦区盈顺路870号3幢1层</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -13317,22 +13317,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13354,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
@@ -13391,12 +13391,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
@@ -13450,17 +13450,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
@@ -13482,17 +13482,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
@@ -13546,17 +13546,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
@@ -13578,17 +13578,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13610,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
@@ -13647,12 +13647,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
@@ -13706,17 +13706,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,29 +13758,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
@@ -13807,12 +13807,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -13866,17 +13866,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -13903,12 +13903,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
@@ -13930,17 +13930,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
@@ -14053,22 +14053,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
@@ -14149,22 +14149,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14186,17 +14186,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14213,22 +14213,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14282,17 +14282,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,22 +14309,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14341,22 +14341,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14405,22 +14405,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14442,17 +14442,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,29 +14462,29 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14494,29 +14494,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,29 +14526,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -14570,17 +14570,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10718,7 +10718,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
+          <t>小鹏汽车广州璟泰大厦销售中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>广州市海珠区阅江西路518号103铺</t>
+          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州璟泰大厦销售中心</t>
+          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
+          <t>广州市海珠区阅江西路518号103铺</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12067,12 +12067,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12483,12 +12483,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -13317,22 +13317,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13354,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13386,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13406,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
@@ -13477,22 +13477,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,14 +13502,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -13519,12 +13519,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13534,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,29 +13566,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,29 +13630,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13662,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,29 +13694,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13726,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
@@ -13770,17 +13770,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,29 +13790,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
@@ -13834,17 +13834,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,29 +13854,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,29 +13886,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,29 +13918,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,29 +13950,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,29 +13982,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,29 +14014,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
@@ -14122,17 +14122,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14149,22 +14149,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14181,22 +14181,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14245,22 +14245,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14277,7 +14277,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,7 +14309,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -14319,12 +14319,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14341,22 +14341,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14405,22 +14405,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -14506,17 +14506,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,29 +14526,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4379,24 +4379,24 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>-2</v>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -4407,38 +4407,38 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C168" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D167" s="4" t="n">
+      <c r="D168" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E168" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -4449,14 +4449,14 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E169" s="3" t="n">
         <v>0</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E170" s="3" t="n">
         <v>0</v>
@@ -4491,14 +4491,14 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E171" s="3" t="n">
         <v>0</v>
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E172" s="3" t="n">
         <v>0</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E173" s="3" t="n">
         <v>0</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="E174" s="3" t="n">
         <v>0</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="E175" s="3" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E176" s="3" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="E177" s="3" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="E178" s="3" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="E179" s="3" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E181" s="3" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E182" s="3" t="n">
         <v>0</v>
@@ -4743,38 +4743,38 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E183" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
           <t>青海</t>
         </is>
       </c>
-      <c r="C183" s="3" t="n">
+      <c r="C184" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="D184" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E183" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D184" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="E184" s="2" t="n">
-        <v>1</v>
+      <c r="E184" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>1</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>1</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>1</v>
@@ -4848,14 +4848,14 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>1</v>
@@ -4869,14 +4869,14 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>1</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>1</v>
@@ -4911,17 +4911,17 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>2</v>
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>2</v>
@@ -4974,17 +4974,17 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -4995,14 +4995,14 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>3</v>
@@ -5016,38 +5016,38 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="D197" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="E197" s="4" t="n">
-        <v>-2</v>
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D198" s="4" t="n">
         <v>29</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="199">
@@ -5079,38 +5079,38 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E199" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="A200" s="4" t="inlineStr">
         <is>
           <t>小鹏</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E200" s="3" t="n">
-        <v>0</v>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="201">
@@ -5121,14 +5121,14 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E201" s="3" t="n">
         <v>0</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E202" s="3" t="n">
         <v>0</v>
@@ -5163,14 +5163,14 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C203" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E203" s="3" t="n">
         <v>0</v>
@@ -5184,14 +5184,14 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C204" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E204" s="3" t="n">
         <v>0</v>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C205" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E205" s="3" t="n">
         <v>0</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C206" s="3" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E206" s="3" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C207" s="3" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E207" s="3" t="n">
         <v>0</v>
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E208" s="3" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E209" s="3" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="E210" s="3" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C211" s="3" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="E211" s="3" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E212" s="3" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E213" s="3" t="n">
         <v>0</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C214" s="3" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="E214" s="3" t="n">
         <v>0</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="E215" s="3" t="n">
         <v>0</v>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C216" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E216" s="3" t="n">
         <v>0</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C217" s="3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E217" s="3" t="n">
         <v>0</v>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E218" s="3" t="n">
         <v>0</v>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C219" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E219" s="3" t="n">
         <v>0</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C220" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E220" s="3" t="n">
         <v>0</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C221" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E221" s="3" t="n">
         <v>0</v>
@@ -5562,14 +5562,14 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C222" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E222" s="3" t="n">
         <v>0</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C223" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E223" s="3" t="n">
         <v>0</v>
@@ -5604,38 +5604,38 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C224" s="3" t="n">
+      <c r="C225" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="D225" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E224" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D225" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E225" s="2" t="n">
-        <v>1</v>
+      <c r="E225" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -5646,59 +5646,59 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D226" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
+      <c r="C227" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="D226" s="2" t="n">
+      <c r="D227" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="E226" s="2" t="n">
+      <c r="E227" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
+      <c r="B228" s="4" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C227" s="4" t="n">
+      <c r="C228" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D227" s="4" t="n">
+      <c r="D228" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E227" s="4" t="n">
+      <c r="E228" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="E228" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C229" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E229" s="3" t="n">
         <v>0</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C230" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E230" s="3" t="n">
         <v>0</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C231" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E231" s="3" t="n">
         <v>0</v>
@@ -5772,14 +5772,14 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C232" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E232" s="3" t="n">
         <v>0</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C233" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E233" s="3" t="n">
         <v>0</v>
@@ -5814,14 +5814,14 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E234" s="3" t="n">
         <v>0</v>
@@ -5835,14 +5835,14 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C235" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E235" s="3" t="n">
         <v>0</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C236" s="3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E236" s="3" t="n">
         <v>0</v>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C237" s="3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E237" s="3" t="n">
         <v>0</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E238" s="3" t="n">
         <v>0</v>
@@ -5919,14 +5919,14 @@
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C239" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E239" s="3" t="n">
         <v>0</v>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C240" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E240" s="3" t="n">
         <v>0</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C241" s="3" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E241" s="3" t="n">
         <v>0</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C242" s="3" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E242" s="3" t="n">
         <v>0</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C243" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E243" s="3" t="n">
         <v>0</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C244" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E244" s="3" t="n">
         <v>0</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C245" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E245" s="3" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C246" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E246" s="3" t="n">
         <v>0</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C247" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E247" s="3" t="n">
         <v>0</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E248" s="3" t="n">
         <v>0</v>
@@ -6129,14 +6129,14 @@
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E249" s="3" t="n">
         <v>0</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C250" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E250" s="3" t="n">
         <v>0</v>
@@ -6171,14 +6171,14 @@
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C251" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E251" s="3" t="n">
         <v>0</v>
@@ -6192,14 +6192,14 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C252" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E252" s="3" t="n">
         <v>0</v>
@@ -6213,14 +6213,14 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C253" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E253" s="3" t="n">
         <v>0</v>
@@ -6234,14 +6234,14 @@
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C254" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E254" s="3" t="n">
         <v>0</v>
@@ -6255,14 +6255,14 @@
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C255" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E255" s="3" t="n">
         <v>0</v>
@@ -6276,59 +6276,59 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>沃尔沃</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C256" s="3" t="n">
+      <c r="C257" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="D257" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E256" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+      <c r="E257" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
+      <c r="C258" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D257" s="2" t="n">
+      <c r="D258" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E257" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D258" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" s="3" t="n">
-        <v>0</v>
+      <c r="E258" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C259" s="3" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C260" s="3" t="n">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C261" s="3" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C262" s="3" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C263" s="3" t="n">
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="3" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C265" s="3" t="n">
@@ -6486,14 +6486,14 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C266" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E266" s="3" t="n">
         <v>0</v>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="3" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -6633,59 +6633,59 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B275" s="4" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C274" s="4" t="n">
+      <c r="C275" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="D274" s="4" t="n">
+      <c r="D275" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E274" s="4" t="n">
+      <c r="E275" s="4" t="n">
         <v>-2</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C275" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="D275" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="E275" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E276" s="3" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C277" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D277" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E277" s="3" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" s="3" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D281" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="E288" s="3" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E289" s="3" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E298" s="3" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E299" s="3" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E300" s="3" t="n">
         <v>0</v>
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E301" s="3" t="n">
         <v>0</v>
@@ -7242,14 +7242,14 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E302" s="3" t="n">
         <v>0</v>
@@ -7263,59 +7263,59 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C303" s="3" t="n">
+      <c r="C304" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="D304" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E303" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
+      <c r="E304" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="C305" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="D304" s="2" t="n">
+      <c r="D305" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="E304" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="4" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="4" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C305" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D305" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="E305" s="4" t="n">
-        <v>-1</v>
+      <c r="E305" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C306" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D306" s="4" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E306" s="4" t="n">
         <v>-1</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C307" s="4" t="n">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="D307" s="4" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="E307" s="4" t="n">
         <v>-1</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C308" s="4" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E308" s="4" t="n">
         <v>-1</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C309" s="4" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D309" s="4" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E309" s="4" t="n">
         <v>-1</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C310" s="4" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D310" s="4" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="E310" s="4" t="n">
         <v>-1</v>
@@ -7431,38 +7431,38 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C311" s="4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D311" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E311" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="inlineStr">
+      <c r="A312" s="4" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C312" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D312" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="E312" s="3" t="n">
-        <v>0</v>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="E312" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="313">
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E313" s="3" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E314" s="3" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D327" s="3" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E327" s="3" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,38 +7851,38 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C331" s="3" t="n">
+      <c r="C332" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="D332" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="E331" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B332" s="2" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C332" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D332" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E332" s="2" t="n">
-        <v>1</v>
+      <c r="E332" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>1</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>1</v>
@@ -7935,59 +7935,59 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
           <t>辽宁</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C336" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D335" s="2" t="n">
+      <c r="D336" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="E335" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="4" t="inlineStr">
+      <c r="E336" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B336" s="4" t="inlineStr">
+      <c r="B337" s="4" t="inlineStr">
         <is>
           <t>河南</t>
         </is>
       </c>
-      <c r="C336" s="4" t="n">
+      <c r="C337" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="D336" s="4" t="n">
+      <c r="D337" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="E336" s="4" t="n">
+      <c r="E337" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="3" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B337" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C337" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="D337" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E337" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E338" s="3" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E340" s="3" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E359" s="3" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E360" s="3" t="n">
         <v>0</v>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E362" s="3" t="n">
         <v>0</v>
@@ -8523,38 +8523,38 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C363" s="3" t="n">
+      <c r="C364" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D363" s="3" t="n">
+      <c r="D364" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E363" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B364" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C364" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="D364" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="E364" s="2" t="n">
-        <v>1</v>
+      <c r="E364" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -8565,38 +8565,38 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="D365" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C365" s="2" t="n">
+      <c r="C366" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D365" s="2" t="n">
+      <c r="D366" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E365" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B366" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C366" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D366" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E366" s="3" t="n">
-        <v>0</v>
+      <c r="E366" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="3" t="n">
         <v>0</v>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E369" s="3" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="3" t="n">
         <v>0</v>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="3" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E375" s="3" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E376" s="3" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D400" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E400" s="3" t="n">
         <v>0</v>
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D401" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E401" s="3" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C403" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D403" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E403" s="3" t="n">
         <v>0</v>
@@ -9384,38 +9384,38 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="3" t="n">
+      <c r="C405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="3" t="n">
+      <c r="D405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="4" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C405" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="D405" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="E405" s="4" t="n">
-        <v>-3</v>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,17 +9426,17 @@
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C406" s="4" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="407">
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E407" s="4" t="n">
         <v>-2</v>
@@ -9468,17 +9468,17 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C408" s="4" t="n">
         <v>79</v>
       </c>
       <c r="D408" s="4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E408" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="409">
@@ -9489,38 +9489,38 @@
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C409" s="4" t="n">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="E409" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="inlineStr">
+      <c r="A410" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C410" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="D410" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E410" s="3" t="n">
-        <v>0</v>
+      <c r="B410" s="4" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="D410" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D423" s="3" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E423" s="3" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D424" s="3" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E424" s="3" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D425" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E425" s="3" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D426" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E426" s="3" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C427" s="3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D427" s="3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E427" s="3" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D428" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E428" s="3" t="n">
         <v>0</v>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C429" s="3" t="n">
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C430" s="3" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D430" s="3" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E430" s="3" t="n">
         <v>0</v>
@@ -9951,38 +9951,38 @@
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E431" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C431" s="3" t="n">
+      <c r="C432" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D431" s="3" t="n">
+      <c r="D432" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="E431" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B432" s="2" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C432" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="D432" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E432" s="2" t="n">
-        <v>1</v>
+      <c r="E432" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -9993,17 +9993,17 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E433" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>181</v>
+        <v>25</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>183</v>
+        <v>27</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>2</v>
@@ -10035,16 +10035,37 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C435" s="2" t="n">
+      <c r="C436" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D435" s="2" t="n">
+      <c r="D436" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="E435" s="2" t="n">
+      <c r="E436" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -10211,12 +10232,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Xiamen</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10590,7 +10611,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10605,7 +10626,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
+          <t>浙江省宁波市海曙区环城南路西段2558号</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10622,7 +10643,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10637,7 +10658,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区环城南路西段2558号</t>
+          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10718,7 +10739,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10733,7 +10754,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10750,7 +10771,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10765,7 +10786,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11870,7 +11891,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11885,7 +11906,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11902,7 +11923,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11917,7 +11938,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12052,7 +12073,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12067,12 +12088,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12105,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12099,12 +12120,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12393,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>北京湾里王府井</t>
+          <t>北京怀柔万达广场</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12387,12 +12408,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
+          <t>北京市怀柔区府前西街1号院1号楼1F</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 13 期</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12425,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>北京怀柔万达广场</t>
+          <t>北京湾里王府井</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -12419,12 +12440,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>北京市怀柔区府前西街1号院1号楼1F</t>
+          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -13317,22 +13338,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13342,29 +13363,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13374,7 +13395,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -13386,17 +13407,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13406,29 +13427,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13438,29 +13459,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13470,29 +13491,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13502,14 +13523,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -13519,12 +13540,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13534,29 +13555,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13566,29 +13587,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13598,29 +13619,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13630,7 +13651,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
@@ -13642,17 +13663,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13662,29 +13683,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13694,7 +13715,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
@@ -13706,17 +13727,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13726,29 +13747,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13758,14 +13779,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13775,12 +13796,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13790,29 +13811,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13822,29 +13843,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13854,29 +13875,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13886,7 +13907,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
@@ -13898,17 +13919,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13918,7 +13939,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -13935,12 +13956,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13950,7 +13971,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -13967,12 +13988,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13982,29 +14003,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14014,29 +14035,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14046,29 +14067,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14078,7 +14099,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
@@ -14117,22 +14138,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14149,22 +14170,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14181,22 +14202,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14218,17 +14239,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14277,22 +14298,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14309,7 +14330,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -14319,12 +14340,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14341,22 +14362,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14405,22 +14426,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14430,29 +14451,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14462,7 +14483,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -14506,17 +14527,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14526,29 +14547,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14558,29 +14579,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14590,7 +14611,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -12073,7 +12073,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>北京怀柔万达广场</t>
+          <t>北京湾里王府井</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>北京市怀柔区府前西街1号院1号楼1F</t>
+          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>北京湾里王府井</t>
+          <t>北京怀柔万达广场</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
+          <t>北京市怀柔区府前西街1号院1号楼1F</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 13 期</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
@@ -13599,17 +13599,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -13754,22 +13754,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13779,14 +13779,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -13796,12 +13796,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
@@ -13914,22 +13914,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14035,14 +14035,14 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
@@ -14138,22 +14138,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14170,22 +14170,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14298,7 +14298,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -14308,12 +14308,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14330,22 +14330,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14362,22 +14362,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14547,29 +14547,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14579,29 +14579,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>北京湾里王府井</t>
+          <t>北京怀柔万达广场</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
+          <t>北京市怀柔区府前西街1号院1号楼1F</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 13 期</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>北京怀柔万达广场</t>
+          <t>北京湾里王府井</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>北京市怀柔区府前西街1号院1号楼1F</t>
+          <t>北京市通州区颐瑞东路66号1号楼1025A铺位</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>连续在档 13 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
+          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>上海市嘉定区澄浏中路886号</t>
+          <t>上海市青浦区盈顺路870号3幢1层</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海盈顺路</t>
+          <t>鸿蒙智行尚界用户中心•上海澄浏中路</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>上海市青浦区盈顺路870号3幢1层</t>
+          <t>上海市嘉定区澄浏中路886号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -13338,22 +13338,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
@@ -13375,17 +13375,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
@@ -13434,22 +13434,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
@@ -13540,12 +13540,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13811,14 +13811,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
@@ -13882,22 +13882,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
@@ -14138,22 +14138,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14170,22 +14170,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14451,29 +14451,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14547,29 +14547,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14579,29 +14579,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13779,29 +13779,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13811,29 +13811,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13875,14 +13875,14 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -13892,12 +13892,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13939,29 +13939,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14234,22 +14234,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车汕尾城区海汕公路零售中心</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14266,7 +14266,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14330,22 +14330,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>理想汽车汕尾城区授权钣喷中心（华逸通店）</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>理想汽车汕尾城区海汕公路零售中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14362,22 +14362,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14451,29 +14451,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14547,29 +14547,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14579,29 +14579,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260817_vs_20260824.xlsx
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
+          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区环城南路西段2558号</t>
+          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省宁波市慈溪市慈溪爱琴海</t>
+          <t>小米汽车浙江省宁波市城南路西段汽车园区</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市慈溪市新城大道北路和北三环东路交汇处爱琴海铺位号F1N009</t>
+          <t>浙江省宁波市海曙区环城南路西段2558号</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
+          <t>小米汽车贵州省贵阳市新添大道</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>贵州省贵阳市花溪区小河万科商场一层</t>
+          <t>新添大道北段60号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车贵州省贵阳市新添大道</t>
+          <t>小米汽车贵州省贵阳市花溪区贵阳小河万科</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>新添大道北段60号</t>
+          <t>贵州省贵阳市花溪区小河万科商场一层</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州璟泰大厦销售中心</t>
+          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
+          <t>广州市海珠区阅江西路518号103铺</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小鹏汽车广州海珠啤酒厂1985销售中心</t>
+          <t>小鹏汽车广州璟泰大厦销售中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>广州市海珠区阅江西路518号103铺</t>
+          <t>广州市越秀区梅花村街道杨箕社区广州大道中295</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州福和万达</t>
+          <t>华为智能生活馆•福州仓山万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
+          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•福州仓山万达广场</t>
+          <t>华为智能生活馆•福州福和万达</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>福建省福州市仓山区金山街道浦上大道 272 号仓山万达广场 A 区（A1- A4）A01 商场室内步行街 1F 层 1-50、151AA 号商铺</t>
+          <t>福建省福州市福清市音西街道福和路福和万达广场1号门旁华为智能生活馆</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区之心城</t>
+          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>之心城购物中心1F</t>
+          <t>包公大道与燎原路交口西北侧</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>连续在档 4 期</t>
+          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市肥东县包公大道服务中心</t>
+          <t>小米汽车安徽省合肥市蜀山区之心城</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>包公大道与燎原路交口西北侧</t>
+          <t>之心城购物中心1F</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期；本期存在高相似店名「小米汽车安徽省合肥市肥东县包公大道零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 4 期</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
+          <t>理想汽车曲靖三江大道零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
+          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>连续在档 16 期</t>
+          <t>连续在档 9 期</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车曲靖三江大道零售中心</t>
+          <t>理想汽车曲靖三江大道服务中心（三江大道临时店）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>曲靖市经济技术开发区三江大道以南瑞和南路以东</t>
+          <t>曲靖市麒麟区经济技术开发区三江大道21号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>连续在档 9 期</t>
+          <t>连续在档 16 期</t>
         </is>
       </c>
     </row>
@@ -13338,22 +13338,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车十堰东风大道销售服务中心</t>
+          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
+          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保定东二环销售服务中心</t>
+          <t>理想汽车深圳布吉万象汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
+          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车西安西咸万象城零售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
+          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
+          <t>理想汽车温州瓯海交付中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
+          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
+          <t>小鹏汽车昆明世博园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
+          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
         </is>
       </c>
     </row>
@@ -13530,22 +13530,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>广州科学城特斯拉中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号 → 上海市杨浦区内江路303号</t>
+          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车佛山顺德交付中心</t>
+          <t>蔚来中心 | 上海合生汇</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
+          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
+          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
+          <t>理想汽车南京江北虹悦城零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
+          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
+          <t>理想汽车南京仙林万达茂零售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
+          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广安品信汽车园销售服务中心</t>
+          <t>小米之家江苏省苏州市常熟市常熟万达汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
+          <t>珠海路8号 → 江苏省苏州市常熟市珠海路8号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>合肥利之星汽车服务有限公司</t>
+          <t>理想汽车苏州吴中永旺梦乐城零售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
+          <t>江苏省苏州市吴中区越溪苏震桃路188号 → 江苏省苏州市吴中区越溪苏震桃路188 号理想汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -13764,12 +13764,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>广州科学城特斯拉中心</t>
+          <t>理想汽车佛山顺德交付中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门 (请从南翔二路中公交车站旁出入口进出) → 广东省广州市黄埔区科学城南翔一路50号新银河世纪跨境电商产业园南门</t>
+          <t>佛山顺德区陈村镇工业园工业大道东1号 → 佛山市顺德区陈村镇顺联机械城16座理想汽车佛山顺德交付中心</t>
         </is>
       </c>
     </row>
@@ -13796,12 +13796,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
+          <t>理想汽车江门江海授权钣喷中心（博腾店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
+          <t>江门市江海区银帆路2号5幢 → 广东省江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
@@ -13828,12 +13828,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车义乌北苑销售服务中心</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13843,29 +13843,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
+          <t>浙江省温州市乐清市城南街道伯乐东路666号南虹广场L-36 → 浙江省乐清市宴海西路777号（乐清市银泰正大广场）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>蔚来中心 | 上海合生汇</t>
+          <t>小鹏汽车保定东二环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13875,29 +13875,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区翔殷路1099号L1层L1-16A、16B，L1-17 → 上海市杨浦区翔殷路 1099 号合生汇 L1-16A、L1-16B、L1-17、L1-18A、L1-18B</t>
+          <t>河北省保定市莲池区东二环422号贺阳中学北行500米路西 → 保定市莲池区东二环422号贺阳中学北行500米路西</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京江北虹悦城零售中心</t>
+          <t>小鹏汽车十堰东风大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13907,29 +13907,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区龙华路1号江北虹悦城1F31号理想汽车 → 江苏省南京市浦口区龙华路1号</t>
+          <t>湖北省十堰市茅箭区东风大道31号 → 湖北省十堰市茅箭区东风大道19号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车海口美兰授权钣喷中心（华悦通店）</t>
+          <t>合肥利之星汽车服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>海南省海口市美兰区灵山镇广州安淼维修厂海口鑫和顺驾驶培训有限公司附近 → 海南省海口市美兰区琼山大道232号军平汽车城</t>
+          <t>经济技术开发区繁华大道18号 → 合肥市经开区繁华大道与芙蓉路交叉口</t>
         </is>
       </c>
     </row>
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州瓯海交付中心</t>
+          <t>理想汽车西安西咸万象城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13971,29 +13971,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市瓯海区娄桥街道瓯海中心站前单元B15地块5号楼 → 温州市瓯海区秀浦路与今汇路交叉路口理想汽车</t>
+          <t>陕西省西安市未央区三桥新街西咸万象城1层1L105商铺 → 陕西省西安市西咸新区沣东新城三桥新街华润西咸万象城1FL155</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳布吉万象汇零售中心</t>
+          <t>小鹏汽车娄底湘阳街汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -14003,29 +14003,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区布吉街道罗岗社区万象汇商场L154 → 广东省深圳市龙岗区布吉街道翔鸽路2号布吉万象汇商场1栋L195号</t>
+          <t>娄底市娄星区檀香路与湘阳街交汇处 → 娄底市娄星区湘阳街与檀香路交汇处</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏南京市浦口区慧成街授权服务中心</t>
+          <t>小鹏汽车义乌北苑销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -14035,29 +14035,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区慧成街3-75号 → 江苏省南京市浦口区雨合路15号</t>
+          <t>浙江省金华市义乌市北苑路300号 → 浙江省义乌市 北苑路 300 号 （十亿客创业园内）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车昆明世博园销售服务中心</t>
+          <t>理想汽车深圳光明蓝鲸世界零售展厅</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -14067,29 +14067,29 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>云南省昆明市盘龙区白龙路522号 → 云南省昆明市盘龙区青云街道白龙路522号</t>
+          <t>广东省深圳市光明区凤凰街道东坑社区龙光玖龙台6栋C座G-35 → 广东省深圳市光明区光明蓝鲸世界G层G35（凤凰城地铁站A口出，顶峰茶餐厅旁边）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南京仙林万达茂零售展厅</t>
+          <t>小鹏汽车广安品信汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市栖霞区仙林大道 181 号南京仙林万达茂 → 江苏省南京市栖霞区仙林大道181号‌‌万达茂1楼理想汽车</t>
+          <t>广安市广安区广安区广武路160号 → 广安市广安区广武路160号</t>
         </is>
       </c>
     </row>
@@ -14138,22 +14138,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1037</t>
+          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>佛山王府井紫薇港体验店L1038</t>
+          <t>理想汽车长沙开福授权服务中心（国理店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权钣喷中心（国理店）</t>
+          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车长沙开福授权服务中心（国理店）</t>
+          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14202,22 +14202,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海长江西路</t>
+          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•上海申江路</t>
+          <t>小鹏汽车郑州高新销售中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14234,7 +14234,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州梧桐街汽车园销售中心</t>
+          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车郑州高新销售中心</t>
+          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权钣喷中心（盛世店）</t>
+          <t>佛山王府井紫薇港体验店L1037</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>理想汽车漯河源汇授权服务中心（盛世店）</t>
+          <t>佛山王府井紫薇港体验店L1038</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14298,22 +14298,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义服务中心（孝义府前街临时店）</t>
+          <t>华为授权体验店（正大广场）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车吕梁孝义授权钣喷中心（晋鹏捷店）</t>
+          <t>华为授权体验店（乐清银泰）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（正大广场）</t>
+          <t>鸿蒙智行授权用户中心•上海长江西路</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（乐清银泰）</t>
+          <t>鸿蒙智行授权用户中心•上海申江路</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区威高广场</t>
+          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省威海市环翠区至海港湾</t>
+          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾万达零售中心</t>
+          <t>理想汽车南通如皋万达零售中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车宜宾零售中心</t>
+          <t>理想汽车南通如皋汽车城零售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14483,7 +14483,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 80%</t>
         </is>
       </c>
     </row>
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋万达零售中心</t>
+          <t>理想汽车北京东坝万达零售展厅</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南通如皋汽车城零售中心</t>
+          <t>理想汽车北京通州万达零售中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 80%</t>
+          <t>店名相似度 83%</t>
         </is>
       </c>
     </row>
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省佛山市南海区南海万达汽车体验店</t>
+          <t>小米汽车山东省威海市环翠区威高广场</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省佛山市南海区佛山南海万达</t>
+          <t>小米汽车山东省威海市环翠区至海港湾</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14547,29 +14547,29 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>理想汽车宜宾万达零售中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区重庆永川纵达城</t>
+          <t>理想汽车宜宾零售中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14579,29 +14579,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 84%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京东坝万达零售展厅</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车北京通州万达零售中心</t>
+          <t>小米汽车重庆市永川区重庆永川纵达城</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 83%</t>
+          <t>店名相似度 84%</t>
         </is>
       </c>
     </row>
